--- a/data/trans_dic/LAWTONB_2R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/LAWTONB_2R3-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 10,21</t>
+          <t>3,88; 10,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,65; 13,26</t>
+          <t>6,48; 14,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 9,34</t>
+          <t>4,06; 9,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,41; 9,51</t>
+          <t>5,23; 9,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,91; 13,41</t>
+          <t>7,15; 13,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,16; 14,88</t>
+          <t>8,04; 15,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,77; 13,11</t>
+          <t>6,7; 12,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,77; 10,3</t>
+          <t>8,15; 12,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,24; 10,74</t>
+          <t>6,15; 10,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,29; 13,23</t>
+          <t>8,27; 13,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,24; 10,41</t>
+          <t>6,22; 10,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 9,16</t>
+          <t>6,99; 10,13</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,9; 27,55</t>
+          <t>16,87; 27,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,01; 41,19</t>
+          <t>28,41; 41,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,72; 31,69</t>
+          <t>21,22; 31,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,53; 33,22</t>
+          <t>23,82; 31,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,24; 32,5</t>
+          <t>22,5; 32,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,31; 45,25</t>
+          <t>34,99; 45,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,71; 43,2</t>
+          <t>31,26; 42,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>42,9; 49,51</t>
+          <t>42,63; 49,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,73; 29,34</t>
+          <t>21,8; 29,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,8; 41,75</t>
+          <t>33,8; 41,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,01; 36,84</t>
+          <t>29,02; 37,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,43; 41,85</t>
+          <t>36,24; 41,46</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,21; 16,0</t>
+          <t>10,51; 16,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,41; 24,6</t>
+          <t>17,04; 24,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,23; 17,94</t>
+          <t>12,53; 17,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,37; 19,18</t>
+          <t>13,78; 18,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,61; 21,66</t>
+          <t>15,63; 21,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,26; 30,1</t>
+          <t>23,09; 29,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,58; 27,28</t>
+          <t>20,29; 27,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,0; 29,15</t>
+          <t>26,28; 30,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,97; 18,37</t>
+          <t>13,99; 18,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,38; 26,34</t>
+          <t>21,61; 26,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,73; 22,37</t>
+          <t>17,67; 22,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,69; 23,87</t>
+          <t>21,4; 24,62</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26455</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39073</t>
+          <t>43930</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65528</t>
+          <t>72052</t>
         </is>
       </c>
     </row>
@@ -1363,62 +1363,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11970; 29886</t>
+          <t>11351; 29762</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20606; 41075</t>
+          <t>20087; 43409</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13365; 31228</t>
+          <t>13573; 32550</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19701; 34644</t>
+          <t>21066; 37211</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23694; 45999</t>
+          <t>24514; 45672</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28886; 52668</t>
+          <t>28464; 55003</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25576; 49513</t>
+          <t>25297; 47381</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16818; 62495</t>
+          <t>35657; 53788</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39675; 68272</t>
+          <t>39099; 66253</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55031; 87790</t>
+          <t>54874; 90031</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44451; 74105</t>
+          <t>44281; 74432</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34056; 88908</t>
+          <t>58744; 85173</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80176</t>
+          <t>85417</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>195003</t>
+          <t>211452</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>275179</t>
+          <t>296868</t>
         </is>
       </c>
     </row>
@@ -1571,62 +1571,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35479; 57825</t>
+          <t>35404; 58257</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69987; 102909</t>
+          <t>70986; 104754</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55832; 81432</t>
+          <t>54527; 80550</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68659; 93001</t>
+          <t>73158; 97871</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74257; 108507</t>
+          <t>75115; 108695</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>137363; 176012</t>
+          <t>136110; 175373</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>126897; 172869</t>
+          <t>125106; 169034</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>181293; 209228</t>
+          <t>196486; 227245</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>118147; 159566</t>
+          <t>118569; 160326</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>215914; 266743</t>
+          <t>215952; 268072</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>190676; 242129</t>
+          <t>190724; 243362</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>255962; 294002</t>
+          <t>278285; 318391</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>106631</t>
+          <t>113539</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>234077</t>
+          <t>255382</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>340708</t>
+          <t>368920</t>
         </is>
       </c>
     </row>
@@ -1779,62 +1779,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>51284; 80384</t>
+          <t>52804; 81300</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>97438; 137651</t>
+          <t>95353; 138893</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72292; 106074</t>
+          <t>74075; 106225</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92603; 123621</t>
+          <t>97888; 130066</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>105642; 146624</t>
+          <t>105823; 147711</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>172810; 223623</t>
+          <t>171588; 219962</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>160121; 212250</t>
+          <t>157849; 210046</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>123513; 300052</t>
+          <t>236056; 274210</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164711; 216682</t>
+          <t>164992; 215710</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>278494; 343070</t>
+          <t>281438; 342188</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>242771; 306347</t>
+          <t>241978; 303179</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>229064; 399571</t>
+          <t>344204; 396063</t>
         </is>
       </c>
     </row>
